--- a/Perf/speedup/06int_time.xlsx
+++ b/Perf/speedup/06int_time.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A19CC5-6CD5-45E4-A89B-360C1C6FF5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5BB05-0C6C-4EC8-B883-D583E545092A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ref" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>vm-small</t>
   </si>
@@ -72,6 +73,22 @@
   </si>
   <si>
     <t>473</t>
+  </si>
+  <si>
+    <t>Perf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perf error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pin error %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -156,6 +173,2094 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2006 INT</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$3:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$3:$N$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>15.590255750986861</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.944407403665572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.691387024996367</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29.393511477266582</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.139466072671986</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24.964754356469545</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.943144207289333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-692A-4DEC-9249-DAA5CBCE92CD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$3:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$3:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20.224687057439422</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.983699544440341</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.433869670257518</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.797675510216781</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6639202313760029</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.892551531535098</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.3807314292997859</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-692A-4DEC-9249-DAA5CBCE92CD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="328894240"/>
+        <c:axId val="328895200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="328894240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328895200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="328895200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328894240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>2006 INT</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Perf error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$3:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$3:$N$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>15.590255750986861</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.944407403665572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.691387024996367</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29.393511477266582</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.139466072671986</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24.964754356469545</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.943144207289333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A42F-4441-BD25-34A26B2382EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pin error %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$L$3:$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$3:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20.224687057439422</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.983699544440341</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.433869670257518</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.797675510216781</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6639202313760029</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.892551531535098</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.3807314292997859</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A42F-4441-BD25-34A26B2382EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="328894240"/>
+        <c:axId val="328895200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="328894240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328895200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="328895200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328894240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>119743</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>163285</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{035F7E63-53AD-5284-2E50-27FAAF1B185B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>119743</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>163285</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECEA857D-F518-4BCA-9065-688C70CD02B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,10 +2548,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,7 +2565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -492,8 +2597,20 @@
         <f>AVERAGE(F2:H2)</f>
         <v>1.3084268196629143</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -510,23 +2627,42 @@
         <v>0.93950259000000003</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F11" si="0">B3/C3</f>
+        <f t="shared" ref="F3:F10" si="0">B3/C3</f>
         <v>1.2088968384758694</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G11" si="1">B3/D3</f>
+        <f t="shared" ref="G3:G10" si="1">B3/D3</f>
         <v>1.1162090495495167</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H11" si="2">B3/E3</f>
+        <f t="shared" ref="H3:H10" si="2">B3/E3</f>
         <v>0.93310950531812797</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="3">AVERAGE(F3:H3)</f>
+        <f t="shared" ref="I3:I10" si="3">AVERAGE(F3:H3)</f>
         <v>1.0860717977811714</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <f>AVERAGE(AVERAGE(I3,I8),AVERAGE(I2,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.5558598202389875</v>
+      </c>
+      <c r="N3">
+        <f>100*ABS(M3-1.843223)/1.843223</f>
+        <v>15.590255750986861</v>
+      </c>
+      <c r="O3">
+        <f>AVERAGE(I8,AVERAGE(I2,I3,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.4704369164792535</v>
+      </c>
+      <c r="P3">
+        <f>100*ABS(O3-1.843223)/1.843223</f>
+        <v>20.224687057439422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -558,8 +2694,27 @@
         <f t="shared" si="3"/>
         <v>0.93255509094880562</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.3834419455219333</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N9" si="4">100*ABS(M4-1.843223)/1.843223</f>
+        <v>24.944407403665572</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGE(I8,I5,AVERAGE(I2,I3,I4,I6,I7,I9,I10))</f>
+        <v>2.5249150562540197</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P9" si="5">100*ABS(O4-1.843223)/1.843223</f>
+        <v>36.983699544440341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -591,8 +2746,27 @@
         <f t="shared" si="3"/>
         <v>5.0812276853434737</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I9),AVERAGE(I7,I10))</f>
+        <v>1.3881056753362513</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="4"/>
+        <v>24.691387024996367</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(I8,I5,I6,AVERAGE(I2,I3,I4,I7,I9,I10))</f>
+        <v>2.1830003255522108</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="5"/>
+        <v>18.433869670257518</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -624,8 +2798,27 @@
         <f t="shared" si="3"/>
         <v>1.0882319823313196</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I9),I7,I10)</f>
+        <v>1.3014350359433826</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>29.393511477266582</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(I8,I5,I6,AVERAGE(I4,I7,I10),AVERAGE(I2,I3,I9))</f>
+        <v>2.0606804684696831</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>11.797675510216781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -657,8 +2850,27 @@
         <f t="shared" si="3"/>
         <v>0.92158362282070916</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(I3,I8,I4,AVERAGE(I2,I5,I6,I9),I7,I10)</f>
+        <v>1.3061176592713133</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>29.139466072671986</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(I8,I5,I6,I4,AVERAGE(I7,I10),AVERAGE(I2,I3,I9))</f>
+        <v>1.8738927604063758</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>1.6639202313760029</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -690,8 +2902,27 @@
         <f t="shared" si="3"/>
         <v>0.99114059439447921</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGE(I3,I8,I4,I2,AVERAGE(I5,I6,I9),I7,I10)</f>
+        <v>1.3830669058080514</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>24.964754356469545</v>
+      </c>
+      <c r="O8">
+        <f>AVERAGE(I8,I5,I6,I4,AVERAGE(I7,I10),AVERAGE(I2,I3),I9)</f>
+        <v>2.0624292451161073</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>11.892551531535098</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -723,8 +2954,27 @@
         <f t="shared" si="3"/>
         <v>4.191847575700721</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGE(I3,I8,I4,I2,AVERAGE(I5,I9),I6,I7,I10)</f>
+        <v>1.4940586090480754</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>18.943144207289333</v>
+      </c>
+      <c r="O9">
+        <f>AVERAGE(I8,I5,I6,I4,I7,I10,AVERAGE(I2,I3),I9)</f>
+        <v>1.9239696492730824</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>4.3807314292997859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -757,14 +3007,543 @@
         <v>0.9879213339231071</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I13">
         <f>AVERAGE(I2:I11)</f>
         <v>1.8432229447674113</v>
       </c>
     </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF7C277-430D-4BC5-B18B-09E6F01B1406}">
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>2.2629353449999998</v>
+      </c>
+      <c r="C2">
+        <v>299</v>
+      </c>
+      <c r="D2">
+        <v>1.7146564259999999</v>
+      </c>
+      <c r="E2">
+        <v>1.9125389429999999</v>
+      </c>
+      <c r="F2">
+        <f>B2/C2</f>
+        <v>7.5683456354515045E-3</v>
+      </c>
+      <c r="G2">
+        <f>B2/D2</f>
+        <v>1.3197602217483539</v>
+      </c>
+      <c r="H2">
+        <f>B2/E2</f>
+        <v>1.1832100743791234</v>
+      </c>
+      <c r="I2">
+        <f>AVERAGE(F2:H2)</f>
+        <v>0.83684621392097636</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0.87665879700000005</v>
+      </c>
+      <c r="C3">
+        <v>152</v>
+      </c>
+      <c r="D3">
+        <v>0.78538943699999997</v>
+      </c>
+      <c r="E3">
+        <v>0.93950259000000003</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F10" si="0">B3/C3</f>
+        <v>5.767492085526316E-3</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G10" si="1">B3/D3</f>
+        <v>1.1162090495495167</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H10" si="2">B3/E3</f>
+        <v>0.93310950531812797</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I10" si="3">AVERAGE(F3:H3)</f>
+        <v>0.68502868231772374</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <f>AVERAGE(AVERAGE(I3,I8),AVERAGE(I2,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.1919875094604324</v>
+      </c>
+      <c r="N3">
+        <f>100*ABS(M3-1.843223)/1.843223</f>
+        <v>35.331345721031454</v>
+      </c>
+      <c r="O3">
+        <f>AVERAGE(I8,AVERAGE(I2,I3,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.1099937988256745</v>
+      </c>
+      <c r="P3">
+        <f>100*ABS(O3-1.843223)/1.843223</f>
+        <v>39.779733715037494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1.511039926</v>
+      </c>
+      <c r="C4">
+        <v>136</v>
+      </c>
+      <c r="D4">
+        <v>1.5957071759999999</v>
+      </c>
+      <c r="E4">
+        <v>2.0874167830000001</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.111058769117647E-2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>0.94694060960969206</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>0.72388031863400037</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="3"/>
+        <v>0.56064383864495626</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I7,I9,I10))</f>
+        <v>1.0119648738991327</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N9" si="4">100*ABS(M4-1.843223)/1.843223</f>
+        <v>45.098076906639477</v>
+      </c>
+      <c r="O4">
+        <f>AVERAGE(I8,I5,AVERAGE(I2,I3,I4,I6,I7,I9,I10))</f>
+        <v>2.1823862897383903</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P9" si="5">100*ABS(O4-1.843223)/1.843223</f>
+        <v>18.400556510980511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0.106965239</v>
+      </c>
+      <c r="C5">
+        <v>260</v>
+      </c>
+      <c r="D5">
+        <v>1.3570021999999999E-2</v>
+      </c>
+      <c r="E5">
+        <v>1.6553900999999999E-2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>4.1140476538461542E-4</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>7.8824661448596034</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>6.4616333636403898</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>4.7815036377551259</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I9),AVERAGE(I7,I10))</f>
+        <v>1.0196136665375517</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="4"/>
+        <v>44.68310852579684</v>
+      </c>
+      <c r="O5">
+        <f>AVERAGE(I8,I5,I6,AVERAGE(I2,I3,I4,I7,I9,I10))</f>
+        <v>1.8324967150631433</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="5"/>
+        <v>0.58193094036135551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1.9071052100000001</v>
+      </c>
+      <c r="C6">
+        <v>232</v>
+      </c>
+      <c r="D6">
+        <v>1.651011282</v>
+      </c>
+      <c r="E6">
+        <v>1.972717214</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>8.2202810775862077E-3</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>1.1551133725081353</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>0.96674028921410327</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>0.71002464759994155</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>AVERAGE(I3,I8,AVERAGE(I2,I4,I5,I6,I9),I7,I10)</f>
+        <v>0.9322702258950667</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="4"/>
+        <v>49.421734326499468</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(I8,I5,I6,AVERAGE(I4,I7,I10),AVERAGE(I2,I3,I9))</f>
+        <v>1.709926982382947</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="5"/>
+        <v>7.2316815500377878</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>2.6343622610000001</v>
+      </c>
+      <c r="C7">
+        <v>339</v>
+      </c>
+      <c r="D7">
+        <v>2.8015979440000001</v>
+      </c>
+      <c r="E7">
+        <v>3.3045553590000001</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>7.770980120943953E-3</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>0.94030703679014416</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>0.79719114216842513</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>0.58175638635983773</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(I3,I8,I4,AVERAGE(I2,I5,I6,I9),I7,I10)</f>
+        <v>0.93829395962950901</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>49.094929933626638</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(I8,I5,I6,I4,AVERAGE(I7,I10),AVERAGE(I2,I3,I9))</f>
+        <v>1.5196160486866246</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="5"/>
+        <v>17.556581667729596</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>9.0356178590000003</v>
+      </c>
+      <c r="C8">
+        <v>305</v>
+      </c>
+      <c r="D8">
+        <v>9.2437994939999992</v>
+      </c>
+      <c r="E8">
+        <v>10.638551720000001</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2.9624976586885246E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>0.97747878076162009</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>0.84932781235752641</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>0.61881052323534391</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
+        <f>AVERAGE(I3,I8,I4,I2,AVERAGE(I5,I6,I9),I7,I10)</f>
+        <v>1.0077367375286614</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="4"/>
+        <v>45.327465123391939</v>
+      </c>
+      <c r="O8">
+        <f>AVERAGE(I8,I5,I6,I4,AVERAGE(I7,I10),AVERAGE(I2,I3),I9)</f>
+        <v>1.7263418867312725</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="5"/>
+        <v>6.3411271055497638</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>7.8927792999999996E-2</v>
+      </c>
+      <c r="C9">
+        <v>174</v>
+      </c>
+      <c r="D9">
+        <v>1.2120959000000001E-2</v>
+      </c>
+      <c r="E9">
+        <v>1.3855252E-2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>4.5360800574712639E-4</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>6.5116789026346833</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>5.6965974346767565</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>4.069576648439063</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <f>AVERAGE(I3,I8,I4,I2,AVERAGE(I5,I9),I6,I7,I10)</f>
+        <v>1.1253358719332862</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>38.947383364178606</v>
+      </c>
+      <c r="O9">
+        <f>AVERAGE(I8,I5,I6,I4,I7,I10,AVERAGE(I2,I3),I9)</f>
+        <v>1.5834112088055043</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="5"/>
+        <v>14.095515908519788</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>7.2776301840000004</v>
+      </c>
+      <c r="C10">
+        <v>245</v>
+      </c>
+      <c r="D10">
+        <v>8.1107870200000001</v>
+      </c>
+      <c r="E10">
+        <v>8.8200113350000002</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>2.970461299591837E-2</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>0.89727792950973084</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>0.82512707836559718</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>0.58403654029041541</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <f>AVERAGE(I2:I11)</f>
+        <v>1.4920252353959316</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Perf/speedup/06int_time.xlsx
+++ b/Perf/speedup/06int_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTexas\26S\Perf\project\Perf\speedup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5BB05-0C6C-4EC8-B883-D583E545092A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5827E9-4AE1-4766-A4A9-6003DCE7E909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2225,15 +2225,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>119743</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:colOff>92529</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>163285</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2549,9 +2549,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>20.224687057439422</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>36.983699544440341</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>18.433869670257518</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>11.797675510216781</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>1.6639202313760029</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>11.892551531535098</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>4.3807314292997859</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -3007,37 +3007,37 @@
         <v>0.9879213339231071</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I13">
         <f>AVERAGE(I2:I11)</f>
         <v>1.8432229447674113</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
     </row>
   </sheetData>
@@ -3050,9 +3050,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF7C277-430D-4BC5-B18B-09E6F01B1406}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>39.779733715037494</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>18.400556510980511</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>0.58193094036135551</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>7.2316815500377878</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>17.556581667729596</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>6.3411271055497638</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>14.095515908519788</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -3508,37 +3508,47 @@
         <v>0.58403654029041541</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="N11">
+        <f>AVERAGE(N3:N9)</f>
+        <v>43.986291985880641</v>
+      </c>
+      <c r="P11">
+        <f>AVERAGE(P3:P9)</f>
+        <v>14.855303914030896</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I13">
         <f>AVERAGE(I2:I11)</f>
         <v>1.4920252353959316</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
     </row>
   </sheetData>
